--- a/budget_reconciliation/Hours_Budget_Reconciliation_Workbook.xlsx
+++ b/budget_reconciliation/Hours_Budget_Reconciliation_Workbook.xlsx
@@ -23,105 +23,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
-  <si>
-    <t xml:space="preserve">Hours Budget Reconciliation — Finding Hours for Out-of-Scope Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What this is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When an out-of-scope deliverable suddenly needs doing, this workbook tells you where the hours come from. You enter your project's planned / actual / forecast effort in HOURS; it computes the net headroom and, for a new ask, whether it is absorbable internally or needs a change order. Hours/effort only — no dollars, rates, or headcount.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to use it — step by step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On the 'Effort Ledger' sheet, list your deliverables (replace the example rows). PLANNED hours come from the budget / SOW / contract. Enter them in the blue cells.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter ACTUAL hours to date (from timesheets / time tracking) and % complete for each deliverable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter EAC — Estimate At Completion: what each deliverable will REALLY take in total (actual so far + your honest estimate of remaining). If it's tracking to plan, EAC = Planned; if over-running, EAC &gt; Planned; if under, EAC &lt; Planned.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set the CONTINGENCY (management reserve) hours. NET FINDABLE = (total Planned + Contingency) − total EAC computes automatically — that is your honest headroom, netting every under-run against every over-run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go to the 'Find Hours' sheet. Enter the new out-of-scope ask's estimated hours in the blue cell. It tells you the shortfall (if any) and the verdict: absorbable internally, or a change order for the excess.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record the decision: which under-running tasks you reallocated from, how much contingency you drew, and any change order (use the 'Change Order' sheet). Never absorb silently by over-running a task.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The decision tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · Reallocate under-run slack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move budget from deliverables forecasting under plan (EAC &lt; Planned). Safest — it's already yours.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 · Draw contingency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The management reserve exists for this. Drawing it is a decision to record, not a silent move.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 · Defer / re-sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free hours by moving lower-priority in-scope work later, with the PM's agreement on new dates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 · Change order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If a shortfall remains, the work is genuine added scope — raise a change order rather than a silent over-run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colour key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You enter these (hours, % complete, the new ask, contingency).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Values pulled from another sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulas — do not overwrite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effort Ledger (hours) — replace the example rows with your deliverables</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+  <si>
+    <t xml:space="preserve">Hours Budget Reconciliation  —  finding hours for out-of-scope work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When an unplanned deliverable lands (an ad-hoc interim, an extra TLF pack, a sponsor re-run) you have to answer one question: can we absorb this, or is it a change order? This workbook does the arithmetic; the 'FindHours playbook' HTML tells you where every number comes from. HOURS/EFFORT ONLY — no rates, no dollars, no headcount. Hours are what you control on a study and what a change order is written in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The core idea (read this first)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget left is NOT what's left to spend. Planned − Actual looks like a cushion, but most of it is already committed to finishing work in flight. What you can actually redeploy is:      NET FINDABLE = (Σ Planned + Contingency) − Σ EAC      — total budget plus reserve, minus the honest forecast cost of finishing everything already in scope. Only that difference is real, spendable slack. The Effort Ledger computes it for you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The four sheets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Instructions (this sheet).   2) Effort Ledger — one row per task: Planned, Actual, % Complete, EAC, Variance; a contingency row; it totals NET FINDABLE. The delivered rows are a WORKED EXAMPLE — replace them with your tasks.   3) Find Hours — enter a new ask; it returns absorbable vs change-order.   4) Change Order — the draft to send when a shortfall remains.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get PLANNED hours from the project budget / SOW (a task grid by deliverable, often by role). One row per biometrics task on the Effort Ledger. Add the contingency / management reserve as its own row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get ACTUAL hours from the time-tracking system, to a cutoff date. Correct for timesheet lag — add verbal estimates of worked-but-unlogged hours, or every task looks falsely under budget and your slack is a mirage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast each task to completion (EAC) — the TOTAL hours it will take once finished, not the hours to date. Enter % Complete (the workbook estimates EAC = Actual ÷ %) or type EAC directly if you re-estimated bottoms-up. See the EAC methods below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade the slack. Only a REAL under-run is spendable: realized (completed task came in under) = safe; projected (in-progress, forecasting under, enough done to trust) = discount; illusory (early task, low actual only because it hasn't ramped) = NOT slack. Counting illusory slack is the #1 way this math goes wrong.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read NET FINDABLE off the ledger total. Be able to say which task each slack hour comes from and why the under-run is real, before you offer it to a PM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test the new ask on the Find Hours sheet: Shortfall = MAX(0, Need − Net Findable). Verdict = absorbable (0) or change order for X hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimating EAC — pick the method that fits what you know</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Actual + ETC (default): Actual-to-date + your honest estimate-to-complete of the remaining work.   • % complete: EAC = Actual ÷ (% complete) — a task 60% done at 90 h forecasts ≈150 h; assumes effort tracks progress linearly.   • Bottoms-up: Actual + a fresh estimate of each remaining item (e.g. 6 TLFs left × ~4 h).   • Completed: EAC = Actual (task is done) — this is your realized variance. Variance = Planned − EAC: positive = forecasting under (possible slack); negative = forecasting over (a problem to raise, NOT a source of hours).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The find-hours decision tree (work the levers in this order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Reallocate under-run SLACK to the new task — inside your project; you decide it and record which task gave / received.   2) Draw CONTINGENCY — a PM decision to record; once spent it's gone for the next surprise.   3) DEFER / re-sequence lower-priority in-scope work — trades schedule for hours; needs PM/sponsor to agree new dates.   4) CHANGE ORDER for any remaining shortfall — it's added scope; don't absorb it silently. Sequence: raise → lead biostat + PM review → sponsor signs → budget amended → THEN do the work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% synthetic. Hours/effort only — no dollars, rates, ROI, or headcount. Full worked detail + conversation scripts: the 'FindHours playbook' HTML next to this file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effort Ledger (hours) — the rows below are a WORKED EXAMPLE; replace with your deliverables. Blue = you enter; grey = auto.</t>
   </si>
   <si>
     <t xml:space="preserve">Deliverable</t>
@@ -273,7 +231,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +255,51 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FF1F2A44"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF222222"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="15"/>
       <color rgb="FFFFFFFF"/>
@@ -306,22 +309,14 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -370,12 +365,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5597"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -386,7 +387,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
+        <bgColor rgb="FF1F2A44"/>
       </patternFill>
     </fill>
     <fill>
@@ -451,108 +452,140 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -613,16 +646,16 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF0B1020"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF222222"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF2F5597"/>
+      <rgbColor rgb="FF1F2A44"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -809,161 +842,142 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="112"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="118"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B8" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="B12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7"/>
+      <c r="B17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A19" s="7"/>
+      <c r="B19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -983,353 +997,353 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="6" t="n">
+      <c r="A1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="14" t="n">
         <v>78</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="14" t="n">
         <v>78</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="16" t="n">
         <f aca="false">B3-E3</f>
         <v>2</v>
       </c>
-      <c r="G3" s="9"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="16" t="n">
         <f aca="false">B4-E4</f>
         <v>5</v>
       </c>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="6" t="n">
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="15" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="14" t="n">
         <v>128</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="16" t="n">
         <f aca="false">B5-E5</f>
         <v>-8</v>
       </c>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="16" t="n">
         <f aca="false">B6-E6</f>
         <v>10</v>
       </c>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="6" t="n">
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="14" t="n">
         <v>210</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="16" t="n">
         <f aca="false">B7-E7</f>
         <v>-10</v>
       </c>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="6" t="n">
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="15" t="n">
         <v>0.45</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="16" t="n">
         <f aca="false">B8-E8</f>
         <v>10</v>
       </c>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="6" t="n">
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="15" t="n">
         <v>0.55</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="16" t="n">
         <f aca="false">B9-E9</f>
         <v>5</v>
       </c>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="6" t="n">
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="16" t="n">
         <f aca="false">B10-E10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="6" t="n">
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="16" t="n">
         <f aca="false">B11-E11</f>
         <v>5</v>
       </c>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="8" t="str">
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="16" t="str">
         <f aca="false">IF(B12="","",B12-E12)</f>
         <v/>
       </c>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="8" t="str">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="16" t="str">
         <f aca="false">IF(B13="","",B13-E13)</f>
         <v/>
       </c>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="8" t="str">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="16" t="str">
         <f aca="false">IF(B14="","",B14-E14)</f>
         <v/>
       </c>
-      <c r="G14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="8" t="str">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="16" t="str">
         <f aca="false">IF(B15="","",B15-E15)</f>
         <v/>
       </c>
-      <c r="G15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="8" t="str">
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="16" t="str">
         <f aca="false">IF(B16="","",B16-E16)</f>
         <v/>
       </c>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="8" t="str">
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="16" t="str">
         <f aca="false">IF(B17="","",B17-E17)</f>
         <v/>
       </c>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="13" t="n">
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="21" t="n">
         <f aca="false">SUM(B3:B17)</f>
         <v>850</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="21" t="n">
         <f aca="false">SUM(C3:C17)</f>
         <v>513</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="13" t="n">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21" t="n">
         <f aca="false">SUM(E3:E17)</f>
         <v>831</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="21" t="n">
         <f aca="false">B18-E18</f>
         <v>19</v>
       </c>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="6" t="n">
+      <c r="G18" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="14" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="17" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <f aca="false">B18+B20-E18</f>
         <v>59</v>
       </c>
@@ -1357,94 +1371,94 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="6" t="n">
+      <c r="A1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="14" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="20" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="28" t="n">
         <f aca="false">'Effort Ledger'!B18-'Effort Ledger'!E18</f>
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="20" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="28" t="n">
         <f aca="false">'Effort Ledger'!B20</f>
         <v>40</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="20" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="28" t="n">
         <f aca="false">'Effort Ledger'!B21</f>
         <v>59</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="8" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="16" t="n">
         <f aca="false">MAX(0,B3-B7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="21" t="str">
+      <c r="A10" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="29" t="str">
         <f aca="false">IF(B3&lt;=B7,"Absorbable internally - reallocate slack + contingency","Change order needed for "&amp;B9&amp;" h - the rest is added scope")</f>
         <v>Absorbable internally - reallocate slack + contingency</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
-        <v>63</v>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="31" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1470,107 +1484,107 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="33"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="33"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="33"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="33"/>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="33"/>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="33"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="33"/>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="33"/>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="33"/>
+    </row>
+    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="33"/>
+    </row>
+    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="33"/>
+    </row>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="33"/>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
+      <c r="B16" s="33"/>
+    </row>
+    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="25"/>
-    </row>
-    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="25"/>
-    </row>
-    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="25"/>
-    </row>
-    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="25"/>
-    </row>
-    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="25"/>
-    </row>
-    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="25"/>
-    </row>
-    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="25"/>
-    </row>
-    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="25"/>
-    </row>
-    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="25"/>
-    </row>
-    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="25"/>
-    </row>
-    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="25"/>
-    </row>
-    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="25"/>
-    </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="25"/>
-    </row>
-    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="25"/>
+      <c r="B17" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/budget_reconciliation/Hours_Budget_Reconciliation_Workbook.xlsx
+++ b/budget_reconciliation/Hours_Budget_Reconciliation_Workbook.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Hours Budget Reconciliation  —  finding hours for out-of-scope work</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t xml:space="preserve">1) Reallocate under-run SLACK to the new task — inside your project; you decide it and record which task gave / received.   2) Draw CONTINGENCY — a PM decision to record; once spent it's gone for the next surprise.   3) DEFER / re-sequence lower-priority in-scope work — trades schedule for hours; needs PM/sponsor to agree new dates.   4) CHANGE ORDER for any remaining shortfall — it's added scope; don't absorb it silently. Sequence: raise → lead biostat + PM review → sponsor signs → budget amended → THEN do the work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How this connects to your real systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Planned hours come from the project budget / SOW task grid (kept by the PM or project finance, often in the CTMS or a planning workbook): read the biometrics task rows and their budgeted hours.
+• Actual hours come from the company timesheet system (hours logged to the project/task code): pull a report to a cutoff date, then add verbal estimates for worked-but-unlogged hours to correct for timesheet lag.
+• This workbook does not connect to those systems: you export from each and transcribe or paste the numbers here, then it computes net findable and the verdict.
+• The change order this workbook drafts routes through the real contract process (lead biostatistician + PM review, sponsor sign-off, SOW/budget amended), and the work is performed only after that. Everything stays in hours; pricing the effort is the PM's / finance's job, not this tool's.</t>
   </si>
   <si>
     <t xml:space="preserve">100% synthetic. Hours/effort only — no dollars, rates, ROI, or headcount. Full worked detail + conversation scripts: the 'FindHours playbook' HTML next to this file.</t>
@@ -452,7 +461,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -461,39 +470,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -842,7 +847,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -855,7 +860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -868,7 +873,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
@@ -880,7 +885,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -892,7 +897,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -900,7 +905,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -908,7 +913,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -916,7 +921,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -924,7 +929,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -932,7 +937,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -946,7 +951,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
         <v>14</v>
       </c>
@@ -958,24 +963,35 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="10"/>
+      <c r="B19" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="9"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4"/>
+      <c r="B22" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1005,345 +1021,345 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="A1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>25</v>
       </c>
+      <c r="F2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="14" t="n">
+      <c r="A3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="13" t="n">
         <v>78</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="13" t="n">
         <v>78</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="15" t="n">
         <f aca="false">B3-E3</f>
         <v>2</v>
       </c>
-      <c r="G3" s="17"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="14" t="n">
+      <c r="A4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="15" t="n">
         <f aca="false">B4-E4</f>
         <v>5</v>
       </c>
-      <c r="G4" s="17"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="14" t="n">
+      <c r="A5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <v>128</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="15" t="n">
         <f aca="false">B5-E5</f>
         <v>-8</v>
       </c>
-      <c r="G5" s="17"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="14" t="n">
+      <c r="A6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="15" t="n">
         <f aca="false">B6-E6</f>
         <v>10</v>
       </c>
-      <c r="G6" s="17"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="14" t="n">
+      <c r="A7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13" t="n">
         <v>210</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="15" t="n">
         <f aca="false">B7-E7</f>
         <v>-10</v>
       </c>
-      <c r="G7" s="17"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="14" t="n">
+      <c r="A8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="14" t="n">
         <v>0.45</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="15" t="n">
         <f aca="false">B8-E8</f>
         <v>10</v>
       </c>
-      <c r="G8" s="17"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="A9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="14" t="n">
         <v>0.55</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="15" t="n">
         <f aca="false">B9-E9</f>
         <v>5</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="14" t="n">
+      <c r="A10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">B10-E10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="17"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="14" t="n">
+      <c r="A11" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="13" t="n">
         <v>85</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="15" t="n">
         <f aca="false">B11-E11</f>
         <v>5</v>
       </c>
-      <c r="G11" s="17"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="16" t="str">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="15" t="str">
         <f aca="false">IF(B12="","",B12-E12)</f>
         <v/>
       </c>
-      <c r="G12" s="18"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="16" t="str">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="15" t="str">
         <f aca="false">IF(B13="","",B13-E13)</f>
         <v/>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="16" t="str">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="15" t="str">
         <f aca="false">IF(B14="","",B14-E14)</f>
         <v/>
       </c>
-      <c r="G14" s="18"/>
+      <c r="G14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="16" t="str">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="15" t="str">
         <f aca="false">IF(B15="","",B15-E15)</f>
         <v/>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="16" t="str">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="15" t="str">
         <f aca="false">IF(B16="","",B16-E16)</f>
         <v/>
       </c>
-      <c r="G16" s="18"/>
+      <c r="G16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="16" t="str">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="15" t="str">
         <f aca="false">IF(B17="","",B17-E17)</f>
         <v/>
       </c>
-      <c r="G17" s="18"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="21" t="n">
+      <c r="A18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="20" t="n">
         <f aca="false">SUM(B3:B17)</f>
         <v>850</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="20" t="n">
         <f aca="false">SUM(C3:C17)</f>
         <v>513</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="21" t="n">
+      <c r="D18" s="21"/>
+      <c r="E18" s="20" t="n">
         <f aca="false">SUM(E3:E17)</f>
         <v>831</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="20" t="n">
         <f aca="false">B18-E18</f>
         <v>19</v>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="14" t="n">
+      <c r="A20" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="13" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="25" t="n">
+      <c r="A21" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="24" t="n">
         <f aca="false">B18+B20-E18</f>
         <v>59</v>
       </c>
@@ -1376,89 +1392,89 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="A1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="14" t="n">
+      <c r="A3" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="13" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="28" t="n">
+      <c r="A5" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="27" t="n">
         <f aca="false">'Effort Ledger'!B18-'Effort Ledger'!E18</f>
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="28" t="n">
+      <c r="A6" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="27" t="n">
         <f aca="false">'Effort Ledger'!B20</f>
         <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="28" t="n">
+      <c r="A7" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="27" t="n">
         <f aca="false">'Effort Ledger'!B21</f>
         <v>59</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="A9" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">MAX(0,B3-B7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="29" t="str">
+      <c r="A10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="28" t="str">
         <f aca="false">IF(B3&lt;=B7,"Absorbable internally - reallocate slack + contingency","Change order needed for "&amp;B9&amp;" h - the rest is added scope")</f>
         <v>Absorbable internally - reallocate slack + contingency</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>45</v>
+      <c r="A12" s="29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="s">
-        <v>46</v>
+      <c r="A13" s="30" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="s">
-        <v>47</v>
+      <c r="A14" s="30" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="s">
-        <v>48</v>
+      <c r="A15" s="30" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
-        <v>49</v>
+      <c r="A16" s="30" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1489,102 +1505,102 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="A1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="33"/>
+      <c r="A3" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="33"/>
+      <c r="A4" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="32"/>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="33"/>
+      <c r="A5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="33"/>
+      <c r="A6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="33"/>
+      <c r="A7" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="32"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="33"/>
+      <c r="A8" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="33"/>
+      <c r="A9" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="33"/>
+      <c r="A10" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="33"/>
+      <c r="A11" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="33"/>
+      <c r="A12" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="33"/>
+      <c r="A13" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="33"/>
+      <c r="A14" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="33"/>
+      <c r="A15" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="32"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="33"/>
+      <c r="A16" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="33"/>
+      <c r="A17" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
